--- a/data/planting_records.xlsx
+++ b/data/planting_records.xlsx
@@ -9,17 +9,17 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7320"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="10695" windowHeight="7290"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="149">
   <si>
     <t>Date</t>
   </si>
@@ -69,166 +69,13 @@
     <t>Season</t>
   </si>
   <si>
-    <t>2025-06-23</t>
-  </si>
-  <si>
-    <t>DG27004</t>
+    <t>2022-07-26</t>
+  </si>
+  <si>
+    <t>DG16000</t>
   </si>
   <si>
     <t>Sugarcane</t>
-  </si>
-  <si>
-    <t>R579</t>
-  </si>
-  <si>
-    <t>Good seed from DG36000</t>
-  </si>
-  <si>
-    <t>2025/26</t>
-  </si>
-  <si>
-    <t>2025-06-24</t>
-  </si>
-  <si>
-    <t>The real figures at Transporters were two, but we added one manday on light duty due to injury and was assigned to planting activitie</t>
-  </si>
-  <si>
-    <t>2025-06-25</t>
-  </si>
-  <si>
-    <t>DG27003</t>
-  </si>
-  <si>
-    <t>2025-06-26</t>
-  </si>
-  <si>
-    <t>DG27002</t>
-  </si>
-  <si>
-    <t>2025-06-27</t>
-  </si>
-  <si>
-    <t>2025-06-28</t>
-  </si>
-  <si>
-    <t>DG27001</t>
-  </si>
-  <si>
-    <t>2025-06-29</t>
-  </si>
-  <si>
-    <t>2025-07-1</t>
-  </si>
-  <si>
-    <t>DG04006</t>
-  </si>
-  <si>
-    <t>DG04005</t>
-  </si>
-  <si>
-    <t>2025-07-2</t>
-  </si>
-  <si>
-    <t>DG04004</t>
-  </si>
-  <si>
-    <t>2025-07-3</t>
-  </si>
-  <si>
-    <t>2025-07-4</t>
-  </si>
-  <si>
-    <t>2025-07-5</t>
-  </si>
-  <si>
-    <t>DG04003</t>
-  </si>
-  <si>
-    <t>2025-07-6</t>
-  </si>
-  <si>
-    <t>2025-07-7</t>
-  </si>
-  <si>
-    <t>DG04002</t>
-  </si>
-  <si>
-    <t>2025-07-8</t>
-  </si>
-  <si>
-    <t>DG04001</t>
-  </si>
-  <si>
-    <t>2025-07-9</t>
-  </si>
-  <si>
-    <t>2025-09-18</t>
-  </si>
-  <si>
-    <t>DG26000</t>
-  </si>
-  <si>
-    <t>Starting replant activities for DG26000.</t>
-  </si>
-  <si>
-    <t>2025-09-19</t>
-  </si>
-  <si>
-    <t>Good seedcane from DG36003</t>
-  </si>
-  <si>
-    <t>2025-09-20</t>
-  </si>
-  <si>
-    <t>2025-09-21</t>
-  </si>
-  <si>
-    <t>2025-09-22</t>
-  </si>
-  <si>
-    <t>2025-09-23</t>
-  </si>
-  <si>
-    <t>2025-09-24</t>
-  </si>
-  <si>
-    <t>2025-09-25</t>
-  </si>
-  <si>
-    <t>2025-09-26</t>
-  </si>
-  <si>
-    <t>2025-09-27</t>
-  </si>
-  <si>
-    <t>10 bundles good seed from DG36004 finished, the other 5 bundles are from DG05006 very old cane</t>
-  </si>
-  <si>
-    <t>2025-09-28</t>
-  </si>
-  <si>
-    <t>Old seed from DG05006</t>
-  </si>
-  <si>
-    <t>2025-09-29</t>
-  </si>
-  <si>
-    <t>Old seedcane</t>
-  </si>
-  <si>
-    <t>2025-09-30</t>
-  </si>
-  <si>
-    <t>DG26001</t>
-  </si>
-  <si>
-    <t>Finishing planting activities with the same bad seed from DG05006</t>
-  </si>
-  <si>
-    <t>2022-07-26</t>
-  </si>
-  <si>
-    <t>DG16000</t>
   </si>
   <si>
     <t>97F1692</t>
@@ -373,10 +220,253 @@
     <t>DG18005</t>
   </si>
   <si>
-    <t>1.8</t>
-  </si>
-  <si>
-    <t>8</t>
+    <t>2025-06-23</t>
+  </si>
+  <si>
+    <t>DG27004</t>
+  </si>
+  <si>
+    <t>R579</t>
+  </si>
+  <si>
+    <t>Good seed from DG36000</t>
+  </si>
+  <si>
+    <t>2025/26</t>
+  </si>
+  <si>
+    <t>2025-06-24</t>
+  </si>
+  <si>
+    <t>The real figures at Transporters were two, but we added one manday on light duty due to injury and was assigned to planting activitie</t>
+  </si>
+  <si>
+    <t>2025-06-25</t>
+  </si>
+  <si>
+    <t>DG27003</t>
+  </si>
+  <si>
+    <t>2025-06-26</t>
+  </si>
+  <si>
+    <t>DG27002</t>
+  </si>
+  <si>
+    <t>2025-06-27</t>
+  </si>
+  <si>
+    <t>2025-06-28</t>
+  </si>
+  <si>
+    <t>DG27001</t>
+  </si>
+  <si>
+    <t>2025-06-29</t>
+  </si>
+  <si>
+    <t>2025-07-1</t>
+  </si>
+  <si>
+    <t>DG04006</t>
+  </si>
+  <si>
+    <t>DG04005</t>
+  </si>
+  <si>
+    <t>2025-07-2</t>
+  </si>
+  <si>
+    <t>DG04004</t>
+  </si>
+  <si>
+    <t>2025-07-3</t>
+  </si>
+  <si>
+    <t>2025-07-4</t>
+  </si>
+  <si>
+    <t>2025-07-5</t>
+  </si>
+  <si>
+    <t>DG04003</t>
+  </si>
+  <si>
+    <t>2025-07-6</t>
+  </si>
+  <si>
+    <t>2025-07-7</t>
+  </si>
+  <si>
+    <t>DG04002</t>
+  </si>
+  <si>
+    <t>2025-07-8</t>
+  </si>
+  <si>
+    <t>DG04001</t>
+  </si>
+  <si>
+    <t>2025-07-9</t>
+  </si>
+  <si>
+    <t>2025-09-18</t>
+  </si>
+  <si>
+    <t>DG26000</t>
+  </si>
+  <si>
+    <t>Starting replant activities for DG26000.</t>
+  </si>
+  <si>
+    <t>2025-09-19</t>
+  </si>
+  <si>
+    <t>Good seedcane from DG36003</t>
+  </si>
+  <si>
+    <t>2025-09-20</t>
+  </si>
+  <si>
+    <t>2025-09-21</t>
+  </si>
+  <si>
+    <t>2025-09-22</t>
+  </si>
+  <si>
+    <t>2025-09-23</t>
+  </si>
+  <si>
+    <t>2025-09-24</t>
+  </si>
+  <si>
+    <t>2025-09-25</t>
+  </si>
+  <si>
+    <t>2025-09-26</t>
+  </si>
+  <si>
+    <t>2025-09-27</t>
+  </si>
+  <si>
+    <t>10 bundles good seed from DG36004 finished, the other 5 bundles are from DG05006 very old cane</t>
+  </si>
+  <si>
+    <t>2025-09-28</t>
+  </si>
+  <si>
+    <t>Old seed from DG05006</t>
+  </si>
+  <si>
+    <t>2025-09-29</t>
+  </si>
+  <si>
+    <t>Old seedcane</t>
+  </si>
+  <si>
+    <t>2025-09-30</t>
+  </si>
+  <si>
+    <t>DG26001</t>
+  </si>
+  <si>
+    <t>Finishing planting activities with the same bad seed from DG05006</t>
+  </si>
+  <si>
+    <t>2026-06-09</t>
+  </si>
+  <si>
+    <t>DG12000</t>
+  </si>
+  <si>
+    <t>2026/27</t>
+  </si>
+  <si>
+    <t>2026-06-10</t>
+  </si>
+  <si>
+    <t>2026-06-11</t>
+  </si>
+  <si>
+    <t>2026-06-13</t>
+  </si>
+  <si>
+    <t>2026-06-15</t>
+  </si>
+  <si>
+    <t>2026-06-17</t>
+  </si>
+  <si>
+    <t>2026-06-19</t>
+  </si>
+  <si>
+    <t>2026-06-20</t>
+  </si>
+  <si>
+    <t>2026-06-21</t>
+  </si>
+  <si>
+    <t>2026-06-22</t>
+  </si>
+  <si>
+    <t>2026-06-23</t>
+  </si>
+  <si>
+    <t>2026-06-24</t>
+  </si>
+  <si>
+    <t>2026-07-19</t>
+  </si>
+  <si>
+    <t>DG22000</t>
+  </si>
+  <si>
+    <t>2026-07-20</t>
+  </si>
+  <si>
+    <t>2026-07-21</t>
+  </si>
+  <si>
+    <t>2026-07-22</t>
+  </si>
+  <si>
+    <t>2026-07-24</t>
+  </si>
+  <si>
+    <t>2026-07-25</t>
+  </si>
+  <si>
+    <t>2026-07-27</t>
+  </si>
+  <si>
+    <t>2026-07-28</t>
+  </si>
+  <si>
+    <t>2026-07-29</t>
+  </si>
+  <si>
+    <t>2026-07-30</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>2026-08-01</t>
+  </si>
+  <si>
+    <t>2026-08-03</t>
+  </si>
+  <si>
+    <t>2026-08-04</t>
+  </si>
+  <si>
+    <t>2026-08-05</t>
+  </si>
+  <si>
+    <t>1.04</t>
+  </si>
+  <si>
+    <t>9</t>
   </si>
 </sst>
 </file>
@@ -739,8 +829,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P61"/>
+  <dimension ref="A1:P88"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -794,16 +887,16 @@
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>68</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
         <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>70</v>
+        <v>19</v>
       </c>
       <c r="E2">
         <v>1.47</v>
@@ -836,21 +929,21 @@
         <v>40</v>
       </c>
       <c r="P2" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>72</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s">
-        <v>69</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
         <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>70</v>
+        <v>19</v>
       </c>
       <c r="E3">
         <v>2.23</v>
@@ -883,24 +976,24 @@
         <v>60</v>
       </c>
       <c r="O3" t="s">
-        <v>73</v>
+        <v>22</v>
       </c>
       <c r="P3" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s">
-        <v>69</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
         <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>70</v>
+        <v>19</v>
       </c>
       <c r="E4">
         <v>0.65</v>
@@ -933,24 +1026,24 @@
         <v>26</v>
       </c>
       <c r="O4" t="s">
-        <v>75</v>
+        <v>24</v>
       </c>
       <c r="P4" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>26</v>
       </c>
       <c r="C5" t="s">
         <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="E5">
         <v>2.6</v>
@@ -983,24 +1076,24 @@
         <v>75</v>
       </c>
       <c r="O5" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="P5" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>26</v>
       </c>
       <c r="C6" t="s">
         <v>18</v>
       </c>
       <c r="D6" t="s">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="E6">
         <v>2</v>
@@ -1033,21 +1126,21 @@
         <v>63</v>
       </c>
       <c r="P6" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>81</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
         <v>18</v>
       </c>
       <c r="D7" t="s">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="E7">
         <v>3.1</v>
@@ -1080,21 +1173,21 @@
         <v>85</v>
       </c>
       <c r="P7" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>82</v>
+        <v>31</v>
       </c>
       <c r="B8" t="s">
-        <v>77</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s">
         <v>18</v>
       </c>
       <c r="D8" t="s">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="E8">
         <v>2</v>
@@ -1127,21 +1220,21 @@
         <v>61</v>
       </c>
       <c r="P8" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
         <v>18</v>
       </c>
       <c r="D9" t="s">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="E9">
         <v>3.3</v>
@@ -1174,21 +1267,21 @@
         <v>90</v>
       </c>
       <c r="P9" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>84</v>
+        <v>33</v>
       </c>
       <c r="B10" t="s">
-        <v>77</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
         <v>18</v>
       </c>
       <c r="D10" t="s">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="E10">
         <v>1.9</v>
@@ -1221,21 +1314,21 @@
         <v>59</v>
       </c>
       <c r="P10" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="B11" t="s">
-        <v>86</v>
+        <v>35</v>
       </c>
       <c r="C11" t="s">
         <v>18</v>
       </c>
       <c r="D11" t="s">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="E11">
         <v>2</v>
@@ -1268,24 +1361,24 @@
         <v>59</v>
       </c>
       <c r="O11" t="s">
-        <v>75</v>
+        <v>24</v>
       </c>
       <c r="P11" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>87</v>
+        <v>36</v>
       </c>
       <c r="B12" t="s">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="C12" t="s">
         <v>18</v>
       </c>
       <c r="D12" t="s">
-        <v>89</v>
+        <v>38</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -1318,24 +1411,24 @@
         <v>30</v>
       </c>
       <c r="O12" t="s">
-        <v>90</v>
+        <v>39</v>
       </c>
       <c r="P12" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>91</v>
+        <v>40</v>
       </c>
       <c r="B13" t="s">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="C13" t="s">
         <v>18</v>
       </c>
       <c r="D13" t="s">
-        <v>89</v>
+        <v>38</v>
       </c>
       <c r="E13">
         <v>2.5</v>
@@ -1368,21 +1461,21 @@
         <v>70</v>
       </c>
       <c r="P13" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>92</v>
+        <v>41</v>
       </c>
       <c r="B14" t="s">
-        <v>93</v>
+        <v>42</v>
       </c>
       <c r="C14" t="s">
         <v>18</v>
       </c>
       <c r="D14" t="s">
-        <v>89</v>
+        <v>38</v>
       </c>
       <c r="E14">
         <v>1.8</v>
@@ -1415,21 +1508,21 @@
         <v>59</v>
       </c>
       <c r="P14" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>94</v>
+        <v>43</v>
       </c>
       <c r="B15" t="s">
-        <v>93</v>
+        <v>42</v>
       </c>
       <c r="C15" t="s">
         <v>18</v>
       </c>
       <c r="D15" t="s">
-        <v>89</v>
+        <v>38</v>
       </c>
       <c r="E15">
         <v>2.2999999999999998</v>
@@ -1462,21 +1555,21 @@
         <v>69</v>
       </c>
       <c r="P15" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>95</v>
+        <v>44</v>
       </c>
       <c r="B16" t="s">
-        <v>96</v>
+        <v>45</v>
       </c>
       <c r="C16" t="s">
         <v>18</v>
       </c>
       <c r="D16" t="s">
-        <v>89</v>
+        <v>38</v>
       </c>
       <c r="E16">
         <v>1.8</v>
@@ -1509,21 +1602,21 @@
         <v>53</v>
       </c>
       <c r="P16" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>97</v>
+        <v>46</v>
       </c>
       <c r="B17" t="s">
-        <v>98</v>
+        <v>47</v>
       </c>
       <c r="C17" t="s">
         <v>18</v>
       </c>
       <c r="D17" t="s">
-        <v>89</v>
+        <v>38</v>
       </c>
       <c r="E17">
         <v>3.3</v>
@@ -1556,21 +1649,21 @@
         <v>90</v>
       </c>
       <c r="P17" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>99</v>
+        <v>48</v>
       </c>
       <c r="B18" t="s">
-        <v>100</v>
+        <v>49</v>
       </c>
       <c r="C18" t="s">
         <v>18</v>
       </c>
       <c r="D18" t="s">
-        <v>89</v>
+        <v>38</v>
       </c>
       <c r="E18">
         <v>2.8</v>
@@ -1603,21 +1696,21 @@
         <v>78</v>
       </c>
       <c r="P18" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>101</v>
+        <v>50</v>
       </c>
       <c r="B19" t="s">
-        <v>102</v>
+        <v>51</v>
       </c>
       <c r="C19" t="s">
         <v>18</v>
       </c>
       <c r="D19" t="s">
-        <v>89</v>
+        <v>38</v>
       </c>
       <c r="E19">
         <v>0.2</v>
@@ -1650,24 +1743,24 @@
         <v>5</v>
       </c>
       <c r="O19" t="s">
-        <v>75</v>
+        <v>24</v>
       </c>
       <c r="P19" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>103</v>
+        <v>52</v>
       </c>
       <c r="B20" t="s">
-        <v>104</v>
+        <v>53</v>
       </c>
       <c r="C20" t="s">
         <v>18</v>
       </c>
       <c r="D20" t="s">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="E20">
         <v>1.4</v>
@@ -1700,21 +1793,21 @@
         <v>38</v>
       </c>
       <c r="P20" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>105</v>
+        <v>54</v>
       </c>
       <c r="B21" t="s">
-        <v>104</v>
+        <v>53</v>
       </c>
       <c r="C21" t="s">
         <v>18</v>
       </c>
       <c r="D21" t="s">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="E21">
         <v>2.4</v>
@@ -1747,21 +1840,21 @@
         <v>61</v>
       </c>
       <c r="P21" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
       <c r="B22" t="s">
-        <v>104</v>
+        <v>53</v>
       </c>
       <c r="C22" t="s">
         <v>18</v>
       </c>
       <c r="D22" t="s">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="E22">
         <v>2.9</v>
@@ -1794,21 +1887,21 @@
         <v>76</v>
       </c>
       <c r="P22" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>107</v>
+        <v>56</v>
       </c>
       <c r="B23" t="s">
-        <v>108</v>
+        <v>57</v>
       </c>
       <c r="C23" t="s">
         <v>18</v>
       </c>
       <c r="D23" t="s">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="E23">
         <v>2.4</v>
@@ -1841,21 +1934,21 @@
         <v>64</v>
       </c>
       <c r="P23" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>109</v>
+        <v>58</v>
       </c>
       <c r="B24" t="s">
-        <v>110</v>
+        <v>59</v>
       </c>
       <c r="C24" t="s">
         <v>18</v>
       </c>
       <c r="D24" t="s">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="E24">
         <v>1.7</v>
@@ -1888,21 +1981,21 @@
         <v>50</v>
       </c>
       <c r="P24" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>111</v>
+        <v>60</v>
       </c>
       <c r="B25" t="s">
-        <v>112</v>
+        <v>61</v>
       </c>
       <c r="C25" t="s">
         <v>18</v>
       </c>
       <c r="D25" t="s">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="E25">
         <v>1.7</v>
@@ -1935,21 +2028,21 @@
         <v>48</v>
       </c>
       <c r="P25" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="B26" t="s">
-        <v>114</v>
+        <v>63</v>
       </c>
       <c r="C26" t="s">
         <v>18</v>
       </c>
       <c r="D26" t="s">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="E26">
         <v>0.6</v>
@@ -1982,27 +2075,27 @@
         <v>19</v>
       </c>
       <c r="P26" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>115</v>
+        <v>64</v>
       </c>
       <c r="B27" t="s">
-        <v>116</v>
+        <v>65</v>
       </c>
       <c r="C27" t="s">
         <v>18</v>
       </c>
       <c r="D27" t="s">
-        <v>78</v>
-      </c>
-      <c r="E27" t="s">
-        <v>117</v>
-      </c>
-      <c r="F27" t="s">
-        <v>118</v>
+        <v>27</v>
+      </c>
+      <c r="E27">
+        <v>1.8</v>
+      </c>
+      <c r="F27">
+        <v>8</v>
       </c>
       <c r="G27">
         <v>2</v>
@@ -2029,21 +2122,21 @@
         <v>49</v>
       </c>
       <c r="P27" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="B28" t="s">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="C28" t="s">
         <v>18</v>
       </c>
       <c r="D28" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="E28">
         <v>1.83</v>
@@ -2076,24 +2169,24 @@
         <v>34</v>
       </c>
       <c r="O28" t="s">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="P28" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>22</v>
+        <v>71</v>
       </c>
       <c r="B29" t="s">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="C29" t="s">
         <v>18</v>
       </c>
       <c r="D29" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="E29">
         <v>1.38</v>
@@ -2126,24 +2219,24 @@
         <v>51</v>
       </c>
       <c r="O29" t="s">
-        <v>23</v>
+        <v>72</v>
       </c>
       <c r="P29" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="B30" t="s">
-        <v>25</v>
+        <v>74</v>
       </c>
       <c r="C30" t="s">
         <v>18</v>
       </c>
       <c r="D30" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="E30">
         <v>3.01</v>
@@ -2176,21 +2269,21 @@
         <v>70</v>
       </c>
       <c r="P30" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="B31" t="s">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="C31" t="s">
         <v>18</v>
       </c>
       <c r="D31" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="E31">
         <v>1.42</v>
@@ -2223,24 +2316,24 @@
         <v>27</v>
       </c>
       <c r="O31" t="s">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="P31" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="B32" t="s">
-        <v>25</v>
+        <v>74</v>
       </c>
       <c r="C32" t="s">
         <v>18</v>
       </c>
       <c r="D32" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="E32">
         <v>0.11</v>
@@ -2273,21 +2366,21 @@
         <v>6</v>
       </c>
       <c r="P32" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="B33" t="s">
-        <v>27</v>
+        <v>76</v>
       </c>
       <c r="C33" t="s">
         <v>18</v>
       </c>
       <c r="D33" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="E33">
         <v>1.31</v>
@@ -2320,21 +2413,21 @@
         <v>27</v>
       </c>
       <c r="P33" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>28</v>
+        <v>77</v>
       </c>
       <c r="B34" t="s">
-        <v>27</v>
+        <v>76</v>
       </c>
       <c r="C34" t="s">
         <v>18</v>
       </c>
       <c r="D34" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="E34">
         <v>1.83</v>
@@ -2367,24 +2460,24 @@
         <v>49</v>
       </c>
       <c r="O34" t="s">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="P34" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>29</v>
+        <v>78</v>
       </c>
       <c r="B35" t="s">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="C35" t="s">
         <v>18</v>
       </c>
       <c r="D35" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="E35">
         <v>1.64</v>
@@ -2417,24 +2510,24 @@
         <v>47</v>
       </c>
       <c r="O35" t="s">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="P35" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>31</v>
+        <v>80</v>
       </c>
       <c r="B36" t="s">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="C36" t="s">
         <v>18</v>
       </c>
       <c r="D36" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="E36">
         <v>1.466</v>
@@ -2467,24 +2560,24 @@
         <v>34</v>
       </c>
       <c r="O36" t="s">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="P36" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>32</v>
+        <v>81</v>
       </c>
       <c r="B37" t="s">
-        <v>33</v>
+        <v>82</v>
       </c>
       <c r="C37" t="s">
         <v>18</v>
       </c>
       <c r="D37" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="E37">
         <v>0.88</v>
@@ -2517,24 +2610,24 @@
         <v>5</v>
       </c>
       <c r="O37" t="s">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="P37" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>32</v>
+        <v>81</v>
       </c>
       <c r="B38" t="s">
-        <v>34</v>
+        <v>83</v>
       </c>
       <c r="C38" t="s">
         <v>18</v>
       </c>
       <c r="D38" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="E38">
         <v>1.03</v>
@@ -2567,24 +2660,24 @@
         <v>15</v>
       </c>
       <c r="O38" t="s">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="P38" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>35</v>
+        <v>84</v>
       </c>
       <c r="B39" t="s">
-        <v>34</v>
+        <v>83</v>
       </c>
       <c r="C39" t="s">
         <v>18</v>
       </c>
       <c r="D39" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="E39">
         <v>2.0299999999999998</v>
@@ -2617,24 +2710,24 @@
         <v>20</v>
       </c>
       <c r="O39" t="s">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="P39" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>35</v>
+        <v>84</v>
       </c>
       <c r="B40" t="s">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="C40" t="s">
         <v>18</v>
       </c>
       <c r="D40" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="E40">
         <v>0.78</v>
@@ -2667,21 +2760,21 @@
         <v>10</v>
       </c>
       <c r="P40" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>37</v>
+        <v>86</v>
       </c>
       <c r="B41" t="s">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="C41" t="s">
         <v>18</v>
       </c>
       <c r="D41" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="E41">
         <v>1.18</v>
@@ -2714,24 +2807,24 @@
         <v>12</v>
       </c>
       <c r="O41" t="s">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="P41" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>38</v>
+        <v>87</v>
       </c>
       <c r="B42" t="s">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="C42" t="s">
         <v>18</v>
       </c>
       <c r="D42" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="E42">
         <v>1.0900000000000001</v>
@@ -2764,24 +2857,24 @@
         <v>11</v>
       </c>
       <c r="O42" t="s">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="P42" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="B43" t="s">
-        <v>40</v>
+        <v>89</v>
       </c>
       <c r="C43" t="s">
         <v>18</v>
       </c>
       <c r="D43" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="E43">
         <v>0.65</v>
@@ -2814,24 +2907,24 @@
         <v>7</v>
       </c>
       <c r="O43" t="s">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="P43" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>41</v>
+        <v>90</v>
       </c>
       <c r="B44" t="s">
-        <v>40</v>
+        <v>89</v>
       </c>
       <c r="C44" t="s">
         <v>18</v>
       </c>
       <c r="D44" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="E44">
         <v>2.4500000000000002</v>
@@ -2864,24 +2957,24 @@
         <v>26</v>
       </c>
       <c r="O44" t="s">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="P44" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>42</v>
+        <v>91</v>
       </c>
       <c r="B45" t="s">
-        <v>43</v>
+        <v>92</v>
       </c>
       <c r="C45" t="s">
         <v>18</v>
       </c>
       <c r="D45" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="E45">
         <v>2.54</v>
@@ -2914,24 +3007,24 @@
         <v>27</v>
       </c>
       <c r="O45" t="s">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="P45" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>44</v>
+        <v>93</v>
       </c>
       <c r="B46" t="s">
-        <v>43</v>
+        <v>92</v>
       </c>
       <c r="C46" t="s">
         <v>18</v>
       </c>
       <c r="D46" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="E46">
         <v>0.56000000000000005</v>
@@ -2964,21 +3057,21 @@
         <v>6</v>
       </c>
       <c r="P46" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>44</v>
+        <v>93</v>
       </c>
       <c r="B47" t="s">
-        <v>45</v>
+        <v>94</v>
       </c>
       <c r="C47" t="s">
         <v>18</v>
       </c>
       <c r="D47" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="E47">
         <v>1.77</v>
@@ -3011,24 +3104,24 @@
         <v>20</v>
       </c>
       <c r="O47" t="s">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="P47" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="B48" t="s">
-        <v>45</v>
+        <v>94</v>
       </c>
       <c r="C48" t="s">
         <v>18</v>
       </c>
       <c r="D48" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="E48">
         <v>1.38</v>
@@ -3061,24 +3154,24 @@
         <v>15</v>
       </c>
       <c r="O48" t="s">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="P48" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>47</v>
+        <v>96</v>
       </c>
       <c r="B49" t="s">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="C49" t="s">
         <v>18</v>
       </c>
       <c r="D49" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -3111,24 +3204,24 @@
         <v>22</v>
       </c>
       <c r="O49" t="s">
-        <v>49</v>
+        <v>98</v>
       </c>
       <c r="P49" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>50</v>
+        <v>99</v>
       </c>
       <c r="B50" t="s">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="C50" t="s">
         <v>18</v>
       </c>
       <c r="D50" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="E50">
         <v>2.91</v>
@@ -3161,24 +3254,24 @@
         <v>67</v>
       </c>
       <c r="O50" t="s">
-        <v>51</v>
+        <v>100</v>
       </c>
       <c r="P50" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>52</v>
+        <v>101</v>
       </c>
       <c r="B51" t="s">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="C51" t="s">
         <v>18</v>
       </c>
       <c r="D51" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="E51">
         <v>0.82</v>
@@ -3211,21 +3304,21 @@
         <v>44</v>
       </c>
       <c r="P51" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>53</v>
+        <v>102</v>
       </c>
       <c r="B52" t="s">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="C52" t="s">
         <v>18</v>
       </c>
       <c r="D52" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="E52">
         <v>1.18</v>
@@ -3258,21 +3351,21 @@
         <v>55</v>
       </c>
       <c r="P52" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>54</v>
+        <v>103</v>
       </c>
       <c r="B53" t="s">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="C53" t="s">
         <v>18</v>
       </c>
       <c r="D53" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="E53">
         <v>2.1800000000000002</v>
@@ -3305,21 +3398,21 @@
         <v>55</v>
       </c>
       <c r="P53" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>55</v>
+        <v>104</v>
       </c>
       <c r="B54" t="s">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="C54" t="s">
         <v>18</v>
       </c>
       <c r="D54" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="E54">
         <v>2.27</v>
@@ -3352,21 +3445,21 @@
         <v>56</v>
       </c>
       <c r="P54" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>56</v>
+        <v>105</v>
       </c>
       <c r="B55" t="s">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="C55" t="s">
         <v>18</v>
       </c>
       <c r="D55" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="E55">
         <v>1.46</v>
@@ -3399,21 +3492,21 @@
         <v>56</v>
       </c>
       <c r="P55" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="B56" t="s">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="C56" t="s">
         <v>18</v>
       </c>
       <c r="D56" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="E56">
         <v>2</v>
@@ -3446,21 +3539,21 @@
         <v>55</v>
       </c>
       <c r="P56" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>58</v>
+        <v>107</v>
       </c>
       <c r="B57" t="s">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="C57" t="s">
         <v>18</v>
       </c>
       <c r="D57" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="E57">
         <v>1.73</v>
@@ -3493,21 +3586,21 @@
         <v>56</v>
       </c>
       <c r="P57" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>59</v>
+        <v>108</v>
       </c>
       <c r="B58" t="s">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="C58" t="s">
         <v>18</v>
       </c>
       <c r="D58" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="E58">
         <v>3.18</v>
@@ -3540,24 +3633,24 @@
         <v>77</v>
       </c>
       <c r="O58" t="s">
-        <v>60</v>
+        <v>109</v>
       </c>
       <c r="P58" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>61</v>
+        <v>110</v>
       </c>
       <c r="B59" t="s">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="C59" t="s">
         <v>18</v>
       </c>
       <c r="D59" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="E59">
         <v>2.27</v>
@@ -3590,24 +3683,24 @@
         <v>81</v>
       </c>
       <c r="O59" t="s">
-        <v>62</v>
+        <v>111</v>
       </c>
       <c r="P59" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>63</v>
+        <v>112</v>
       </c>
       <c r="B60" t="s">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="C60" t="s">
         <v>18</v>
       </c>
       <c r="D60" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="E60">
         <v>3.09</v>
@@ -3640,24 +3733,24 @@
         <v>78</v>
       </c>
       <c r="O60" t="s">
-        <v>64</v>
+        <v>113</v>
       </c>
       <c r="P60" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="B61" t="s">
-        <v>66</v>
+        <v>115</v>
       </c>
       <c r="C61" t="s">
         <v>18</v>
       </c>
       <c r="D61" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="E61">
         <v>1.55</v>
@@ -3690,16 +3783,1282 @@
         <v>39</v>
       </c>
       <c r="O61" t="s">
-        <v>67</v>
+        <v>116</v>
       </c>
       <c r="P61" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>117</v>
+      </c>
+      <c r="B62" t="s">
+        <v>118</v>
+      </c>
+      <c r="C62" t="s">
+        <v>18</v>
+      </c>
+      <c r="D62" t="s">
+        <v>68</v>
+      </c>
+      <c r="E62">
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="F62">
+        <v>5</v>
+      </c>
+      <c r="G62">
+        <v>2</v>
+      </c>
+      <c r="H62">
+        <v>22</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>1</v>
+      </c>
+      <c r="K62">
+        <v>2</v>
+      </c>
+      <c r="L62">
+        <v>1</v>
+      </c>
+      <c r="M62">
+        <v>2</v>
+      </c>
+      <c r="N62">
+        <v>30</v>
+      </c>
+      <c r="P62" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>120</v>
+      </c>
+      <c r="B63" t="s">
+        <v>118</v>
+      </c>
+      <c r="C63" t="s">
+        <v>18</v>
+      </c>
+      <c r="D63" t="s">
+        <v>68</v>
+      </c>
+      <c r="E63">
+        <v>2.11</v>
+      </c>
+      <c r="F63">
+        <v>6</v>
+      </c>
+      <c r="G63">
+        <v>2</v>
+      </c>
+      <c r="H63">
+        <v>22</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>1</v>
+      </c>
+      <c r="K63">
+        <v>4</v>
+      </c>
+      <c r="L63">
+        <v>1</v>
+      </c>
+      <c r="M63">
+        <v>2</v>
+      </c>
+      <c r="N63">
+        <v>32</v>
+      </c>
+      <c r="P63" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>121</v>
+      </c>
+      <c r="B64" t="s">
+        <v>118</v>
+      </c>
+      <c r="C64" t="s">
+        <v>18</v>
+      </c>
+      <c r="D64" t="s">
+        <v>68</v>
+      </c>
+      <c r="E64">
+        <v>2.0099999999999998</v>
+      </c>
+      <c r="F64">
+        <v>6</v>
+      </c>
+      <c r="G64">
+        <v>2</v>
+      </c>
+      <c r="H64">
         <v>21</v>
       </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>4</v>
+      </c>
+      <c r="K64">
+        <v>3</v>
+      </c>
+      <c r="L64">
+        <v>1</v>
+      </c>
+      <c r="M64">
+        <v>2</v>
+      </c>
+      <c r="N64">
+        <v>33</v>
+      </c>
+      <c r="P64" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>122</v>
+      </c>
+      <c r="B65" t="s">
+        <v>118</v>
+      </c>
+      <c r="C65" t="s">
+        <v>18</v>
+      </c>
+      <c r="D65" t="s">
+        <v>68</v>
+      </c>
+      <c r="E65">
+        <v>2.11</v>
+      </c>
+      <c r="F65">
+        <v>8</v>
+      </c>
+      <c r="G65">
+        <v>2</v>
+      </c>
+      <c r="H65">
+        <v>22</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>2</v>
+      </c>
+      <c r="K65">
+        <v>2</v>
+      </c>
+      <c r="L65">
+        <v>1</v>
+      </c>
+      <c r="M65">
+        <v>2</v>
+      </c>
+      <c r="N65">
+        <v>31</v>
+      </c>
+      <c r="P65" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>123</v>
+      </c>
+      <c r="B66" t="s">
+        <v>118</v>
+      </c>
+      <c r="C66" t="s">
+        <v>18</v>
+      </c>
+      <c r="D66" t="s">
+        <v>68</v>
+      </c>
+      <c r="E66">
+        <v>1.92</v>
+      </c>
+      <c r="F66">
+        <v>5</v>
+      </c>
+      <c r="G66">
+        <v>2</v>
+      </c>
+      <c r="H66">
+        <v>21</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>3</v>
+      </c>
+      <c r="K66">
+        <v>3</v>
+      </c>
+      <c r="L66">
+        <v>1</v>
+      </c>
+      <c r="M66">
+        <v>2</v>
+      </c>
+      <c r="N66">
+        <v>32</v>
+      </c>
+      <c r="P66" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>124</v>
+      </c>
+      <c r="B67" t="s">
+        <v>118</v>
+      </c>
+      <c r="C67" t="s">
+        <v>18</v>
+      </c>
+      <c r="D67" t="s">
+        <v>68</v>
+      </c>
+      <c r="E67">
+        <v>2.0099999999999998</v>
+      </c>
+      <c r="F67">
+        <v>9</v>
+      </c>
+      <c r="G67">
+        <v>2</v>
+      </c>
+      <c r="H67">
+        <v>21</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>4</v>
+      </c>
+      <c r="K67">
+        <v>2</v>
+      </c>
+      <c r="L67">
+        <v>1</v>
+      </c>
+      <c r="M67">
+        <v>2</v>
+      </c>
+      <c r="N67">
+        <v>32</v>
+      </c>
+      <c r="P67" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>125</v>
+      </c>
+      <c r="B68" t="s">
+        <v>118</v>
+      </c>
+      <c r="C68" t="s">
+        <v>18</v>
+      </c>
+      <c r="D68" t="s">
+        <v>68</v>
+      </c>
+      <c r="E68">
+        <v>3.06</v>
+      </c>
+      <c r="F68">
+        <v>9</v>
+      </c>
+      <c r="G68">
+        <v>2</v>
+      </c>
+      <c r="H68">
+        <v>33</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>3</v>
+      </c>
+      <c r="K68">
+        <v>2</v>
+      </c>
+      <c r="L68">
+        <v>1</v>
+      </c>
+      <c r="M68">
+        <v>2</v>
+      </c>
+      <c r="N68">
+        <v>43</v>
+      </c>
+      <c r="P68" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>126</v>
+      </c>
+      <c r="B69" t="s">
+        <v>118</v>
+      </c>
+      <c r="C69" t="s">
+        <v>18</v>
+      </c>
+      <c r="D69" t="s">
+        <v>68</v>
+      </c>
+      <c r="E69">
+        <v>1.05</v>
+      </c>
+      <c r="F69">
+        <v>6</v>
+      </c>
+      <c r="G69">
+        <v>2</v>
+      </c>
+      <c r="H69">
+        <v>12</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>0</v>
+      </c>
+      <c r="K69">
+        <v>2</v>
+      </c>
+      <c r="L69">
+        <v>1</v>
+      </c>
+      <c r="M69">
+        <v>2</v>
+      </c>
+      <c r="N69">
+        <v>19</v>
+      </c>
+      <c r="P69" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>127</v>
+      </c>
+      <c r="B70" t="s">
+        <v>118</v>
+      </c>
+      <c r="C70" t="s">
+        <v>18</v>
+      </c>
+      <c r="D70" t="s">
+        <v>68</v>
+      </c>
+      <c r="E70">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="F70">
+        <v>5</v>
+      </c>
+      <c r="G70">
+        <v>1</v>
+      </c>
+      <c r="H70">
+        <v>3</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>2</v>
+      </c>
+      <c r="K70">
+        <v>1</v>
+      </c>
+      <c r="L70">
+        <v>1</v>
+      </c>
+      <c r="M70">
+        <v>1</v>
+      </c>
+      <c r="N70">
+        <v>9</v>
+      </c>
+      <c r="P70" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>128</v>
+      </c>
+      <c r="B71" t="s">
+        <v>118</v>
+      </c>
+      <c r="C71" t="s">
+        <v>18</v>
+      </c>
+      <c r="D71" t="s">
+        <v>68</v>
+      </c>
+      <c r="E71">
+        <v>3.29</v>
+      </c>
+      <c r="F71">
+        <v>9</v>
+      </c>
+      <c r="G71">
+        <v>2</v>
+      </c>
+      <c r="H71">
+        <v>49</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>3</v>
+      </c>
+      <c r="K71">
+        <v>3</v>
+      </c>
+      <c r="L71">
+        <v>1</v>
+      </c>
+      <c r="M71">
+        <v>2</v>
+      </c>
+      <c r="N71">
+        <v>60</v>
+      </c>
+      <c r="P71" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>129</v>
+      </c>
+      <c r="B72" t="s">
+        <v>118</v>
+      </c>
+      <c r="C72" t="s">
+        <v>18</v>
+      </c>
+      <c r="D72" t="s">
+        <v>68</v>
+      </c>
+      <c r="E72">
+        <v>1.05</v>
+      </c>
+      <c r="F72">
+        <v>6</v>
+      </c>
+      <c r="G72">
+        <v>2</v>
+      </c>
+      <c r="H72">
+        <v>12</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>4</v>
+      </c>
+      <c r="K72">
+        <v>3</v>
+      </c>
+      <c r="L72">
+        <v>1</v>
+      </c>
+      <c r="M72">
+        <v>2</v>
+      </c>
+      <c r="N72">
+        <v>24</v>
+      </c>
+      <c r="P72" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>130</v>
+      </c>
+      <c r="B73" t="s">
+        <v>118</v>
+      </c>
+      <c r="C73" t="s">
+        <v>18</v>
+      </c>
+      <c r="D73" t="s">
+        <v>68</v>
+      </c>
+      <c r="E73">
+        <v>2.54</v>
+      </c>
+      <c r="F73">
+        <v>8</v>
+      </c>
+      <c r="G73">
+        <v>2</v>
+      </c>
+      <c r="H73">
+        <v>28</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>3</v>
+      </c>
+      <c r="K73">
+        <v>4</v>
+      </c>
+      <c r="L73">
+        <v>1</v>
+      </c>
+      <c r="M73">
+        <v>2</v>
+      </c>
+      <c r="N73">
+        <v>40</v>
+      </c>
+      <c r="P73" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>131</v>
+      </c>
+      <c r="B74" t="s">
+        <v>132</v>
+      </c>
+      <c r="C74" t="s">
+        <v>18</v>
+      </c>
+      <c r="D74" t="s">
+        <v>68</v>
+      </c>
+      <c r="E74">
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="F74">
+        <v>9</v>
+      </c>
+      <c r="G74">
+        <v>2</v>
+      </c>
+      <c r="H74">
+        <v>24</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>1</v>
+      </c>
+      <c r="K74">
+        <v>2</v>
+      </c>
+      <c r="L74">
+        <v>1</v>
+      </c>
+      <c r="M74">
+        <v>2</v>
+      </c>
+      <c r="N74">
+        <v>32</v>
+      </c>
+      <c r="P74" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>133</v>
+      </c>
+      <c r="B75" t="s">
+        <v>132</v>
+      </c>
+      <c r="C75" t="s">
+        <v>18</v>
+      </c>
+      <c r="D75" t="s">
+        <v>68</v>
+      </c>
+      <c r="E75">
+        <v>1.68</v>
+      </c>
+      <c r="F75">
+        <v>6</v>
+      </c>
+      <c r="G75">
+        <v>2</v>
+      </c>
+      <c r="H75">
+        <v>23</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>1</v>
+      </c>
+      <c r="K75">
+        <v>1</v>
+      </c>
+      <c r="L75">
+        <v>1</v>
+      </c>
+      <c r="M75">
+        <v>2</v>
+      </c>
+      <c r="N75">
+        <v>30</v>
+      </c>
+      <c r="P75" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>134</v>
+      </c>
+      <c r="B76" t="s">
+        <v>132</v>
+      </c>
+      <c r="C76" t="s">
+        <v>18</v>
+      </c>
+      <c r="D76" t="s">
+        <v>68</v>
+      </c>
+      <c r="E76">
+        <v>1.23</v>
+      </c>
+      <c r="F76">
+        <v>9</v>
+      </c>
+      <c r="G76">
+        <v>2</v>
+      </c>
+      <c r="H76">
+        <v>14</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>1</v>
+      </c>
+      <c r="K76">
+        <v>2</v>
+      </c>
+      <c r="L76">
+        <v>1</v>
+      </c>
+      <c r="M76">
+        <v>2</v>
+      </c>
+      <c r="N76">
+        <v>22</v>
+      </c>
+      <c r="P76" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>135</v>
+      </c>
+      <c r="B77" t="s">
+        <v>132</v>
+      </c>
+      <c r="C77" t="s">
+        <v>18</v>
+      </c>
+      <c r="D77" t="s">
+        <v>68</v>
+      </c>
+      <c r="E77">
+        <v>1.86</v>
+      </c>
+      <c r="F77">
+        <v>12</v>
+      </c>
+      <c r="G77">
+        <v>2</v>
+      </c>
+      <c r="H77">
+        <v>24</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>2</v>
+      </c>
+      <c r="K77">
+        <v>2</v>
+      </c>
+      <c r="L77">
+        <v>1</v>
+      </c>
+      <c r="M77">
+        <v>2</v>
+      </c>
+      <c r="N77">
+        <v>33</v>
+      </c>
+      <c r="P77" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>136</v>
+      </c>
+      <c r="B78" t="s">
+        <v>132</v>
+      </c>
+      <c r="C78" t="s">
+        <v>18</v>
+      </c>
+      <c r="D78" t="s">
+        <v>68</v>
+      </c>
+      <c r="E78">
+        <v>1.77</v>
+      </c>
+      <c r="F78">
+        <v>11</v>
+      </c>
+      <c r="G78">
+        <v>2</v>
+      </c>
+      <c r="H78">
+        <v>24</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>3</v>
+      </c>
+      <c r="K78">
+        <v>2</v>
+      </c>
+      <c r="L78">
+        <v>1</v>
+      </c>
+      <c r="M78">
+        <v>2</v>
+      </c>
+      <c r="N78">
+        <v>34</v>
+      </c>
+      <c r="P78" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>137</v>
+      </c>
+      <c r="B79" t="s">
+        <v>132</v>
+      </c>
+      <c r="C79" t="s">
+        <v>18</v>
+      </c>
+      <c r="D79" t="s">
+        <v>68</v>
+      </c>
+      <c r="E79">
+        <v>1.27</v>
+      </c>
+      <c r="F79">
+        <v>9</v>
+      </c>
+      <c r="G79">
+        <v>2</v>
+      </c>
+      <c r="H79">
+        <v>23</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>2</v>
+      </c>
+      <c r="K79">
+        <v>2</v>
+      </c>
+      <c r="L79">
+        <v>1</v>
+      </c>
+      <c r="M79">
+        <v>2</v>
+      </c>
+      <c r="N79">
+        <v>32</v>
+      </c>
+      <c r="P79" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>138</v>
+      </c>
+      <c r="B80" t="s">
+        <v>132</v>
+      </c>
+      <c r="C80" t="s">
+        <v>18</v>
+      </c>
+      <c r="D80" t="s">
+        <v>68</v>
+      </c>
+      <c r="E80">
+        <v>1.45</v>
+      </c>
+      <c r="F80">
+        <v>9</v>
+      </c>
+      <c r="G80">
+        <v>2</v>
+      </c>
+      <c r="H80">
+        <v>23</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>3</v>
+      </c>
+      <c r="K80">
+        <v>2</v>
+      </c>
+      <c r="L80">
+        <v>1</v>
+      </c>
+      <c r="M80">
+        <v>2</v>
+      </c>
+      <c r="N80">
+        <v>33</v>
+      </c>
+      <c r="P80" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>139</v>
+      </c>
+      <c r="B81" t="s">
+        <v>132</v>
+      </c>
+      <c r="C81" t="s">
+        <v>18</v>
+      </c>
+      <c r="D81" t="s">
+        <v>68</v>
+      </c>
+      <c r="E81">
+        <v>1.23</v>
+      </c>
+      <c r="F81">
+        <v>9</v>
+      </c>
+      <c r="G81">
+        <v>2</v>
+      </c>
+      <c r="H81">
+        <v>22</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>2</v>
+      </c>
+      <c r="K81">
+        <v>2</v>
+      </c>
+      <c r="L81">
+        <v>1</v>
+      </c>
+      <c r="M81">
+        <v>2</v>
+      </c>
+      <c r="N81">
+        <v>31</v>
+      </c>
+      <c r="P81" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>140</v>
+      </c>
+      <c r="B82" t="s">
+        <v>132</v>
+      </c>
+      <c r="C82" t="s">
+        <v>18</v>
+      </c>
+      <c r="D82" t="s">
+        <v>68</v>
+      </c>
+      <c r="E82">
+        <v>1.99</v>
+      </c>
+      <c r="F82">
+        <v>12</v>
+      </c>
+      <c r="G82">
+        <v>2</v>
+      </c>
+      <c r="H82">
+        <v>22</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>3</v>
+      </c>
+      <c r="K82">
+        <v>2</v>
+      </c>
+      <c r="L82">
+        <v>1</v>
+      </c>
+      <c r="M82">
+        <v>2</v>
+      </c>
+      <c r="N82">
+        <v>32</v>
+      </c>
+      <c r="P82" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>141</v>
+      </c>
+      <c r="B83" t="s">
+        <v>132</v>
+      </c>
+      <c r="C83" t="s">
+        <v>18</v>
+      </c>
+      <c r="D83" t="s">
+        <v>68</v>
+      </c>
+      <c r="E83">
+        <v>2.3199999999999998</v>
+      </c>
+      <c r="F83">
+        <v>9</v>
+      </c>
+      <c r="G83">
+        <v>2</v>
+      </c>
+      <c r="H83">
+        <v>26</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>2</v>
+      </c>
+      <c r="K83">
+        <v>2</v>
+      </c>
+      <c r="L83">
+        <v>1</v>
+      </c>
+      <c r="M83">
+        <v>2</v>
+      </c>
+      <c r="N83">
+        <v>35</v>
+      </c>
+      <c r="P83" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>142</v>
+      </c>
+      <c r="B84" t="s">
+        <v>132</v>
+      </c>
+      <c r="C84" t="s">
+        <v>18</v>
+      </c>
+      <c r="D84" t="s">
+        <v>68</v>
+      </c>
+      <c r="E84">
+        <v>1.36</v>
+      </c>
+      <c r="F84">
+        <v>9</v>
+      </c>
+      <c r="G84">
+        <v>2</v>
+      </c>
+      <c r="H84">
+        <v>15</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>2</v>
+      </c>
+      <c r="K84">
+        <v>2</v>
+      </c>
+      <c r="L84">
+        <v>1</v>
+      </c>
+      <c r="M84">
+        <v>2</v>
+      </c>
+      <c r="N84">
+        <v>24</v>
+      </c>
+      <c r="P84" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>143</v>
+      </c>
+      <c r="B85" t="s">
+        <v>132</v>
+      </c>
+      <c r="C85" t="s">
+        <v>18</v>
+      </c>
+      <c r="D85" t="s">
+        <v>68</v>
+      </c>
+      <c r="E85">
+        <v>1.68</v>
+      </c>
+      <c r="F85">
+        <v>12</v>
+      </c>
+      <c r="G85">
+        <v>2</v>
+      </c>
+      <c r="H85">
+        <v>19</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>2</v>
+      </c>
+      <c r="K85">
+        <v>2</v>
+      </c>
+      <c r="L85">
+        <v>1</v>
+      </c>
+      <c r="M85">
+        <v>2</v>
+      </c>
+      <c r="N85">
+        <v>28</v>
+      </c>
+      <c r="P85" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>144</v>
+      </c>
+      <c r="B86" t="s">
+        <v>132</v>
+      </c>
+      <c r="C86" t="s">
+        <v>18</v>
+      </c>
+      <c r="D86" t="s">
+        <v>68</v>
+      </c>
+      <c r="E86">
+        <v>2.09</v>
+      </c>
+      <c r="F86">
+        <v>9</v>
+      </c>
+      <c r="G86">
+        <v>2</v>
+      </c>
+      <c r="H86">
+        <v>24</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>2</v>
+      </c>
+      <c r="K86">
+        <v>2</v>
+      </c>
+      <c r="L86">
+        <v>1</v>
+      </c>
+      <c r="M86">
+        <v>2</v>
+      </c>
+      <c r="N86">
+        <v>33</v>
+      </c>
+      <c r="P86" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>145</v>
+      </c>
+      <c r="B87" t="s">
+        <v>132</v>
+      </c>
+      <c r="C87" t="s">
+        <v>18</v>
+      </c>
+      <c r="D87" t="s">
+        <v>68</v>
+      </c>
+      <c r="E87">
+        <v>1.65</v>
+      </c>
+      <c r="F87">
+        <v>9</v>
+      </c>
+      <c r="G87">
+        <v>2</v>
+      </c>
+      <c r="H87">
+        <v>15</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>2</v>
+      </c>
+      <c r="K87">
+        <v>2</v>
+      </c>
+      <c r="L87">
+        <v>1</v>
+      </c>
+      <c r="M87">
+        <v>2</v>
+      </c>
+      <c r="N87">
+        <v>24</v>
+      </c>
+      <c r="P87" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>146</v>
+      </c>
+      <c r="B88" t="s">
+        <v>132</v>
+      </c>
+      <c r="C88" t="s">
+        <v>18</v>
+      </c>
+      <c r="D88" t="s">
+        <v>68</v>
+      </c>
+      <c r="E88" t="s">
+        <v>147</v>
+      </c>
+      <c r="F88" t="s">
+        <v>148</v>
+      </c>
+      <c r="G88">
+        <v>2</v>
+      </c>
+      <c r="H88">
+        <v>12</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>1</v>
+      </c>
+      <c r="K88">
+        <v>2</v>
+      </c>
+      <c r="L88">
+        <v>1</v>
+      </c>
+      <c r="M88">
+        <v>2</v>
+      </c>
+      <c r="N88">
+        <v>20</v>
+      </c>
+      <c r="P88" t="s">
+        <v>119</v>
+      </c>
     </row>
   </sheetData>
-  <sortState ref="A2:P61">
-    <sortCondition ref="A2"/>
-  </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/planting_records.xlsx
+++ b/data/planting_records.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="172">
   <si>
     <t>Date</t>
   </si>
@@ -418,9 +418,6 @@
     <t>2026-07-19</t>
   </si>
   <si>
-    <t>DG22000</t>
-  </si>
-  <si>
     <t>2026-07-20</t>
   </si>
   <si>
@@ -463,10 +460,82 @@
     <t>2026-08-05</t>
   </si>
   <si>
-    <t>1.04</t>
-  </si>
-  <si>
     <t>9</t>
+  </si>
+  <si>
+    <t>DG22009</t>
+  </si>
+  <si>
+    <t>DG22008</t>
+  </si>
+  <si>
+    <t>DG22007</t>
+  </si>
+  <si>
+    <t>DG22006</t>
+  </si>
+  <si>
+    <t>DG22005</t>
+  </si>
+  <si>
+    <t>DG22004</t>
+  </si>
+  <si>
+    <t>DG22003</t>
+  </si>
+  <si>
+    <t>DG22001</t>
+  </si>
+  <si>
+    <t>DG22002</t>
+  </si>
+  <si>
+    <t>DG26009</t>
+  </si>
+  <si>
+    <t>DG26008</t>
+  </si>
+  <si>
+    <t>DG26007</t>
+  </si>
+  <si>
+    <t>DG26006</t>
+  </si>
+  <si>
+    <t>DG26005</t>
+  </si>
+  <si>
+    <t>DG26004</t>
+  </si>
+  <si>
+    <t>DG26003</t>
+  </si>
+  <si>
+    <t>DG26002</t>
+  </si>
+  <si>
+    <t>DG12001</t>
+  </si>
+  <si>
+    <t>DG12002</t>
+  </si>
+  <si>
+    <t>DG12003</t>
+  </si>
+  <si>
+    <t>DG12004</t>
+  </si>
+  <si>
+    <t>DG12005</t>
+  </si>
+  <si>
+    <t>DG12006</t>
+  </si>
+  <si>
+    <t>DG12007</t>
+  </si>
+  <si>
+    <t>DG12008</t>
   </si>
 </sst>
 </file>
@@ -829,10 +898,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P88"/>
+  <dimension ref="A1:P89"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.140625" customWidth="1"/>
+    <col min="5" max="5" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="122.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
@@ -3215,7 +3299,7 @@
         <v>99</v>
       </c>
       <c r="B50" t="s">
-        <v>97</v>
+        <v>157</v>
       </c>
       <c r="C50" t="s">
         <v>18</v>
@@ -3265,7 +3349,7 @@
         <v>101</v>
       </c>
       <c r="B51" t="s">
-        <v>97</v>
+        <v>156</v>
       </c>
       <c r="C51" t="s">
         <v>18</v>
@@ -3312,7 +3396,7 @@
         <v>102</v>
       </c>
       <c r="B52" t="s">
-        <v>97</v>
+        <v>158</v>
       </c>
       <c r="C52" t="s">
         <v>18</v>
@@ -3359,7 +3443,7 @@
         <v>103</v>
       </c>
       <c r="B53" t="s">
-        <v>97</v>
+        <v>159</v>
       </c>
       <c r="C53" t="s">
         <v>18</v>
@@ -3406,7 +3490,7 @@
         <v>104</v>
       </c>
       <c r="B54" t="s">
-        <v>97</v>
+        <v>160</v>
       </c>
       <c r="C54" t="s">
         <v>18</v>
@@ -3453,7 +3537,7 @@
         <v>105</v>
       </c>
       <c r="B55" t="s">
-        <v>97</v>
+        <v>158</v>
       </c>
       <c r="C55" t="s">
         <v>18</v>
@@ -3500,7 +3584,7 @@
         <v>106</v>
       </c>
       <c r="B56" t="s">
-        <v>97</v>
+        <v>161</v>
       </c>
       <c r="C56" t="s">
         <v>18</v>
@@ -3547,7 +3631,7 @@
         <v>107</v>
       </c>
       <c r="B57" t="s">
-        <v>97</v>
+        <v>162</v>
       </c>
       <c r="C57" t="s">
         <v>18</v>
@@ -3594,7 +3678,7 @@
         <v>108</v>
       </c>
       <c r="B58" t="s">
-        <v>97</v>
+        <v>163</v>
       </c>
       <c r="C58" t="s">
         <v>18</v>
@@ -3794,7 +3878,7 @@
         <v>117</v>
       </c>
       <c r="B62" t="s">
-        <v>118</v>
+        <v>164</v>
       </c>
       <c r="C62" t="s">
         <v>18</v>
@@ -3841,7 +3925,7 @@
         <v>120</v>
       </c>
       <c r="B63" t="s">
-        <v>118</v>
+        <v>165</v>
       </c>
       <c r="C63" t="s">
         <v>18</v>
@@ -3888,7 +3972,7 @@
         <v>121</v>
       </c>
       <c r="B64" t="s">
-        <v>118</v>
+        <v>166</v>
       </c>
       <c r="C64" t="s">
         <v>18</v>
@@ -3935,7 +4019,7 @@
         <v>122</v>
       </c>
       <c r="B65" t="s">
-        <v>118</v>
+        <v>167</v>
       </c>
       <c r="C65" t="s">
         <v>18</v>
@@ -3982,7 +4066,7 @@
         <v>123</v>
       </c>
       <c r="B66" t="s">
-        <v>118</v>
+        <v>168</v>
       </c>
       <c r="C66" t="s">
         <v>18</v>
@@ -4076,7 +4160,7 @@
         <v>125</v>
       </c>
       <c r="B68" t="s">
-        <v>118</v>
+        <v>169</v>
       </c>
       <c r="C68" t="s">
         <v>18</v>
@@ -4123,7 +4207,7 @@
         <v>126</v>
       </c>
       <c r="B69" t="s">
-        <v>118</v>
+        <v>171</v>
       </c>
       <c r="C69" t="s">
         <v>18</v>
@@ -4217,7 +4301,7 @@
         <v>128</v>
       </c>
       <c r="B71" t="s">
-        <v>118</v>
+        <v>170</v>
       </c>
       <c r="C71" t="s">
         <v>18</v>
@@ -4358,7 +4442,7 @@
         <v>131</v>
       </c>
       <c r="B74" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="C74" t="s">
         <v>18</v>
@@ -4367,34 +4451,34 @@
         <v>68</v>
       </c>
       <c r="E74">
-        <v>2.1800000000000002</v>
+        <v>0.36</v>
       </c>
       <c r="F74">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H74">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="I74">
         <v>0</v>
       </c>
       <c r="J74">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K74">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L74">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M74">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N74">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="P74" t="s">
         <v>119</v>
@@ -4402,10 +4486,10 @@
     </row>
     <row r="75" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B75" t="s">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="C75" t="s">
         <v>18</v>
@@ -4414,16 +4498,16 @@
         <v>68</v>
       </c>
       <c r="E75">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="F75">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H75">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I75">
         <v>0</v>
@@ -4432,7 +4516,7 @@
         <v>1</v>
       </c>
       <c r="K75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L75">
         <v>1</v>
@@ -4441,7 +4525,7 @@
         <v>2</v>
       </c>
       <c r="N75">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="P75" t="s">
         <v>119</v>
@@ -4449,10 +4533,10 @@
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B76" t="s">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="C76" t="s">
         <v>18</v>
@@ -4461,16 +4545,16 @@
         <v>68</v>
       </c>
       <c r="E76">
-        <v>1.23</v>
+        <v>1.68</v>
       </c>
       <c r="F76">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G76">
         <v>2</v>
       </c>
       <c r="H76">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="I76">
         <v>0</v>
@@ -4479,7 +4563,7 @@
         <v>1</v>
       </c>
       <c r="K76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L76">
         <v>1</v>
@@ -4488,7 +4572,7 @@
         <v>2</v>
       </c>
       <c r="N76">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="P76" t="s">
         <v>119</v>
@@ -4496,10 +4580,10 @@
     </row>
     <row r="77" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B77" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="C77" t="s">
         <v>18</v>
@@ -4508,22 +4592,22 @@
         <v>68</v>
       </c>
       <c r="E77">
-        <v>1.86</v>
+        <v>1.23</v>
       </c>
       <c r="F77">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G77">
         <v>2</v>
       </c>
       <c r="H77">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="I77">
         <v>0</v>
       </c>
       <c r="J77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K77">
         <v>2</v>
@@ -4535,7 +4619,7 @@
         <v>2</v>
       </c>
       <c r="N77">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="P77" t="s">
         <v>119</v>
@@ -4543,10 +4627,10 @@
     </row>
     <row r="78" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B78" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="C78" t="s">
         <v>18</v>
@@ -4555,10 +4639,10 @@
         <v>68</v>
       </c>
       <c r="E78">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="F78">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G78">
         <v>2</v>
@@ -4570,7 +4654,7 @@
         <v>0</v>
       </c>
       <c r="J78">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K78">
         <v>2</v>
@@ -4582,7 +4666,7 @@
         <v>2</v>
       </c>
       <c r="N78">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P78" t="s">
         <v>119</v>
@@ -4590,10 +4674,10 @@
     </row>
     <row r="79" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B79" t="s">
-        <v>132</v>
+        <v>150</v>
       </c>
       <c r="C79" t="s">
         <v>18</v>
@@ -4602,22 +4686,22 @@
         <v>68</v>
       </c>
       <c r="E79">
-        <v>1.27</v>
+        <v>1.77</v>
       </c>
       <c r="F79">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G79">
         <v>2</v>
       </c>
       <c r="H79">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I79">
         <v>0</v>
       </c>
       <c r="J79">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K79">
         <v>2</v>
@@ -4629,7 +4713,7 @@
         <v>2</v>
       </c>
       <c r="N79">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P79" t="s">
         <v>119</v>
@@ -4637,10 +4721,10 @@
     </row>
     <row r="80" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B80" t="s">
-        <v>132</v>
+        <v>150</v>
       </c>
       <c r="C80" t="s">
         <v>18</v>
@@ -4649,7 +4733,7 @@
         <v>68</v>
       </c>
       <c r="E80">
-        <v>1.45</v>
+        <v>1.27</v>
       </c>
       <c r="F80">
         <v>9</v>
@@ -4664,7 +4748,7 @@
         <v>0</v>
       </c>
       <c r="J80">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K80">
         <v>2</v>
@@ -4676,7 +4760,7 @@
         <v>2</v>
       </c>
       <c r="N80">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P80" t="s">
         <v>119</v>
@@ -4684,10 +4768,10 @@
     </row>
     <row r="81" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B81" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="C81" t="s">
         <v>18</v>
@@ -4696,7 +4780,7 @@
         <v>68</v>
       </c>
       <c r="E81">
-        <v>1.23</v>
+        <v>1.45</v>
       </c>
       <c r="F81">
         <v>9</v>
@@ -4705,13 +4789,13 @@
         <v>2</v>
       </c>
       <c r="H81">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I81">
         <v>0</v>
       </c>
       <c r="J81">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K81">
         <v>2</v>
@@ -4723,7 +4807,7 @@
         <v>2</v>
       </c>
       <c r="N81">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="P81" t="s">
         <v>119</v>
@@ -4731,10 +4815,10 @@
     </row>
     <row r="82" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B82" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="C82" t="s">
         <v>18</v>
@@ -4743,10 +4827,10 @@
         <v>68</v>
       </c>
       <c r="E82">
-        <v>1.99</v>
+        <v>1.23</v>
       </c>
       <c r="F82">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G82">
         <v>2</v>
@@ -4758,7 +4842,7 @@
         <v>0</v>
       </c>
       <c r="J82">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K82">
         <v>2</v>
@@ -4770,7 +4854,7 @@
         <v>2</v>
       </c>
       <c r="N82">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P82" t="s">
         <v>119</v>
@@ -4778,10 +4862,10 @@
     </row>
     <row r="83" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B83" t="s">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="C83" t="s">
         <v>18</v>
@@ -4790,22 +4874,22 @@
         <v>68</v>
       </c>
       <c r="E83">
-        <v>2.3199999999999998</v>
+        <v>1.99</v>
       </c>
       <c r="F83">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G83">
         <v>2</v>
       </c>
       <c r="H83">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="I83">
         <v>0</v>
       </c>
       <c r="J83">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K83">
         <v>2</v>
@@ -4817,7 +4901,7 @@
         <v>2</v>
       </c>
       <c r="N83">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="P83" t="s">
         <v>119</v>
@@ -4825,10 +4909,10 @@
     </row>
     <row r="84" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B84" t="s">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="C84" t="s">
         <v>18</v>
@@ -4837,7 +4921,7 @@
         <v>68</v>
       </c>
       <c r="E84">
-        <v>1.36</v>
+        <v>2.3199999999999998</v>
       </c>
       <c r="F84">
         <v>9</v>
@@ -4846,7 +4930,7 @@
         <v>2</v>
       </c>
       <c r="H84">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="I84">
         <v>0</v>
@@ -4864,7 +4948,7 @@
         <v>2</v>
       </c>
       <c r="N84">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="P84" t="s">
         <v>119</v>
@@ -4872,10 +4956,10 @@
     </row>
     <row r="85" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B85" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="C85" t="s">
         <v>18</v>
@@ -4884,16 +4968,16 @@
         <v>68</v>
       </c>
       <c r="E85">
-        <v>1.68</v>
+        <v>1.36</v>
       </c>
       <c r="F85">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G85">
         <v>2</v>
       </c>
       <c r="H85">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I85">
         <v>0</v>
@@ -4911,7 +4995,7 @@
         <v>2</v>
       </c>
       <c r="N85">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="P85" t="s">
         <v>119</v>
@@ -4919,10 +5003,10 @@
     </row>
     <row r="86" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B86" t="s">
-        <v>132</v>
+        <v>155</v>
       </c>
       <c r="C86" t="s">
         <v>18</v>
@@ -4931,16 +5015,16 @@
         <v>68</v>
       </c>
       <c r="E86">
-        <v>2.09</v>
+        <v>1.68</v>
       </c>
       <c r="F86">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G86">
         <v>2</v>
       </c>
       <c r="H86">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I86">
         <v>0</v>
@@ -4958,7 +5042,7 @@
         <v>2</v>
       </c>
       <c r="N86">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="P86" t="s">
         <v>119</v>
@@ -4966,10 +5050,10 @@
     </row>
     <row r="87" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B87" t="s">
-        <v>132</v>
+        <v>155</v>
       </c>
       <c r="C87" t="s">
         <v>18</v>
@@ -4978,7 +5062,7 @@
         <v>68</v>
       </c>
       <c r="E87">
-        <v>1.65</v>
+        <v>2.09</v>
       </c>
       <c r="F87">
         <v>9</v>
@@ -4987,7 +5071,7 @@
         <v>2</v>
       </c>
       <c r="H87">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="I87">
         <v>0</v>
@@ -5005,7 +5089,7 @@
         <v>2</v>
       </c>
       <c r="N87">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="P87" t="s">
         <v>119</v>
@@ -5013,48 +5097,95 @@
     </row>
     <row r="88" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
+        <v>144</v>
+      </c>
+      <c r="B88" t="s">
+        <v>154</v>
+      </c>
+      <c r="C88" t="s">
+        <v>18</v>
+      </c>
+      <c r="D88" t="s">
+        <v>68</v>
+      </c>
+      <c r="E88">
+        <v>1.65</v>
+      </c>
+      <c r="F88">
+        <v>9</v>
+      </c>
+      <c r="G88">
+        <v>2</v>
+      </c>
+      <c r="H88">
+        <v>15</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>2</v>
+      </c>
+      <c r="K88">
+        <v>2</v>
+      </c>
+      <c r="L88">
+        <v>1</v>
+      </c>
+      <c r="M88">
+        <v>2</v>
+      </c>
+      <c r="N88">
+        <v>24</v>
+      </c>
+      <c r="P88" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>145</v>
+      </c>
+      <c r="B89" t="s">
+        <v>154</v>
+      </c>
+      <c r="C89" t="s">
+        <v>18</v>
+      </c>
+      <c r="D89" t="s">
+        <v>68</v>
+      </c>
+      <c r="E89">
+        <v>1.04</v>
+      </c>
+      <c r="F89" t="s">
         <v>146</v>
       </c>
-      <c r="B88" t="s">
-        <v>132</v>
-      </c>
-      <c r="C88" t="s">
-        <v>18</v>
-      </c>
-      <c r="D88" t="s">
-        <v>68</v>
-      </c>
-      <c r="E88" t="s">
-        <v>147</v>
-      </c>
-      <c r="F88" t="s">
-        <v>148</v>
-      </c>
-      <c r="G88">
-        <v>2</v>
-      </c>
-      <c r="H88">
+      <c r="G89">
+        <v>2</v>
+      </c>
+      <c r="H89">
         <v>12</v>
       </c>
-      <c r="I88">
-        <v>0</v>
-      </c>
-      <c r="J88">
-        <v>1</v>
-      </c>
-      <c r="K88">
-        <v>2</v>
-      </c>
-      <c r="L88">
-        <v>1</v>
-      </c>
-      <c r="M88">
-        <v>2</v>
-      </c>
-      <c r="N88">
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>1</v>
+      </c>
+      <c r="K89">
+        <v>2</v>
+      </c>
+      <c r="L89">
+        <v>1</v>
+      </c>
+      <c r="M89">
+        <v>2</v>
+      </c>
+      <c r="N89">
         <v>20</v>
       </c>
-      <c r="P88" t="s">
+      <c r="P89" t="s">
         <v>119</v>
       </c>
     </row>
